--- a/Result/profitability/8111.xlsx
+++ b/Result/profitability/8111.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13</v>
+        <v>0.16625</v>
       </c>
       <c r="N2" t="n">
-        <v>28.81</v>
+        <v>28.50625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.02</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006250000000000006</v>
+        <v>-0.02250000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>25.17625</v>
+        <v>24.58125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1175</v>
+        <v>-0.11125</v>
       </c>
       <c r="N4" t="n">
-        <v>23.30625</v>
+        <v>22.7675</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2175</v>
+        <v>-0.1175</v>
       </c>
       <c r="N5" t="n">
-        <v>18.32375</v>
+        <v>18.26</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.18125</v>
+        <v>-0.19625</v>
       </c>
       <c r="N6" t="n">
-        <v>15.19625</v>
+        <v>15.23125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.21125</v>
+        <v>-0.22</v>
       </c>
       <c r="N7" t="n">
-        <v>13.50125</v>
+        <v>13.44625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2525</v>
+        <v>-0.24125</v>
       </c>
       <c r="N8" t="n">
-        <v>11.6375</v>
+        <v>11.3925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1774,7 +1774,7 @@
         <v>0.23</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0425</v>
+        <v>-0.04249999999999998</v>
       </c>
       <c r="N11" t="n">
         <v>15.71625</v>
@@ -1901,7 +1901,7 @@
         <v>0.13</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03625</v>
+        <v>0.03625000000000002</v>
       </c>
       <c r="N12" t="n">
         <v>16.18625</v>
@@ -2030,7 +2030,7 @@
         <v>-0.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0975</v>
+        <v>0.09750000000000002</v>
       </c>
       <c r="N13" t="n">
         <v>18.8475</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8111</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>206</v>
+      </c>
+      <c r="D75" t="n">
+        <v>147</v>
+      </c>
+      <c r="E75" t="n">
+        <v>59</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>28</v>
+      </c>
+      <c r="J75" t="n">
+        <v>31</v>
+      </c>
+      <c r="K75" t="n">
+        <v>28</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.15875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.58625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5294117647058822</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.960000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06367771280051981</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.481481481481481</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.509999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01738833958404362</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
